--- a/Result/profitability/1319.xlsx
+++ b/Result/profitability/1319.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.5</v>
       </c>
       <c r="M2" t="n">
-        <v>1.52625</v>
+        <v>1.51</v>
       </c>
       <c r="N2" t="n">
-        <v>32.03</v>
+        <v>32.02500000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.47</v>
       </c>
       <c r="M3" t="n">
-        <v>1.39875</v>
+        <v>1.2975</v>
       </c>
       <c r="N3" t="n">
-        <v>31.06875</v>
+        <v>30.82125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.44</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1825</v>
+        <v>1.0425</v>
       </c>
       <c r="N4" t="n">
-        <v>29.44125</v>
+        <v>28.74625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8537499999999999</v>
+        <v>0.9275</v>
       </c>
       <c r="N5" t="n">
-        <v>26.5975</v>
+        <v>26.535</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.77</v>
       </c>
       <c r="M6" t="n">
-        <v>0.85375</v>
+        <v>0.885</v>
       </c>
       <c r="N6" t="n">
-        <v>25.85375</v>
+        <v>26.42</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.65</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7962499999999999</v>
+        <v>0.7075</v>
       </c>
       <c r="N7" t="n">
-        <v>25.78625</v>
+        <v>25.6425</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6637500000000001</v>
+        <v>0.6312500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>24.9725</v>
+        <v>24.975</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1319</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5663</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3821</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1842</v>
+      </c>
+      <c r="F75" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="G75" t="n">
+        <v>892</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>15.76%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>97</v>
+      </c>
+      <c r="J75" t="n">
+        <v>990</v>
+      </c>
+      <c r="K75" t="n">
+        <v>807</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.63375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>33.115</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1604938271604939</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.02000000000000313</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.0006151953245157049</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.5900000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.7662337662337664</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01513775355737212</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
